--- a/punjab_eprocurement.xlsx
+++ b/punjab_eprocurement.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>372.</t>
+          <t>390.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/punjab_eprocurement.xlsx
+++ b/punjab_eprocurement.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,47 +490,105 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>40</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>137.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>15-Jun-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>29-Jun-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>30-Jun-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1,10,00,000</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>11000000</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Review Tender</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Punjab eProcurement</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>32</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>390.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>608.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>10-Jun-2026 05:00 PM</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>24-Jun-2026 05:00 PM</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>25-Jun-2026 11:00 AM</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>1,67,51,919</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K3" t="n">
         <v>16751919</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2F%2Ft7YZXMaRvO80hFY4Uwmw%3D%3D</t>
         </is>

--- a/punjab_eprocurement.xlsx
+++ b/punjab_eprocurement.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>137.</t>
+          <t>196.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>608.</t>
+          <t>655.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/punjab_eprocurement.xlsx
+++ b/punjab_eprocurement.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>196.</t>
+          <t>328.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>655.</t>
+          <t>781.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/punjab_eprocurement.xlsx
+++ b/punjab_eprocurement.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>328.</t>
+          <t>698.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>781.</t>
+          <t>1091.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/punjab_eprocurement.xlsx
+++ b/punjab_eprocurement.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>698.</t>
+          <t>714.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1091.</t>
+          <t>1108.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/punjab_eprocurement.xlsx
+++ b/punjab_eprocurement.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>714.</t>
+          <t>882.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1108.</t>
+          <t>1248.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/punjab_eprocurement.xlsx
+++ b/punjab_eprocurement.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>882.</t>
+          <t>886.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1248.</t>
+          <t>1252.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/punjab_eprocurement.xlsx
+++ b/punjab_eprocurement.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>886.</t>
+          <t>942.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1252.</t>
+          <t>1293.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/punjab_eprocurement.xlsx
+++ b/punjab_eprocurement.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>942.</t>
+          <t>1004.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1293.</t>
+          <t>1230.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/punjab_eprocurement.xlsx
+++ b/punjab_eprocurement.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1004.</t>
+          <t>1037.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1230.</t>
+          <t>1256.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/punjab_eprocurement.xlsx
+++ b/punjab_eprocurement.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1037.</t>
+          <t>1325.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -533,64 +533,6 @@
       <c r="L2" t="inlineStr">
         <is>
           <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Review Tender</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Punjab eProcurement</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1256.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>10-Jun-2026 05:00 PM</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>24-Jun-2026 05:00 PM</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>25-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>[CONSTRUCTION OF COMMUNITY HALL NEAR CHURCH CIVIL LINE AT HOSHIARPUR (PUNJAB)] [11][2026_CEPW_169887_1]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>CE-PWD(B and R)||Construction Circle-Hoshiarpur||Provincial Division-Hoshiarpur</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1,67,51,919</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>16751919</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S%2F%2Ft7YZXMaRvO80hFY4Uwmw%3D%3D</t>
         </is>
       </c>
     </row>

--- a/punjab_eprocurement.xlsx
+++ b/punjab_eprocurement.xlsx
@@ -494,45 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1325.</t>
+          <t>836.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15-Jun-2026 09:00 AM</t>
+          <t>20-Jun-2026 09:00 AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29-Jun-2026 01:00 PM</t>
+          <t>13-Jul-2026 11:30 AM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>30-Jun-2026 09:00 AM</t>
+          <t>13-Jul-2026 12:30 PM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[Construction of Building and playground of Govt. Sen. Sec. School (Girls) main bazar, Bhargo Camp.] [MCJ/(B and R) 2026-27/09][2026_DLG_169930_63]</t>
+          <t>[Construction of Govt ITI Building G plus 5 Centre of Excellence at Nangal Distt Ropar ] [Tender Notice No. 9 Dated 19.06.2026][2026_CEPW_170505_1]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Department of Local Government||Director - Local Government||Municipal Corporation - Jalandhar||B and R</t>
+          <t>CE-PWD(B and R)||Construction Circle-Chandigarh||Construction Division-Ropar</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1,10,00,000</t>
+          <t>19,43,71,801</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>11000000</v>
+        <v>194371801</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=So%2F7JtzasXBC3D2YwSvhRtw%3D%3D</t>
+          <t>https://eproc.punjab.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S6W2ferMHIsjtTQZh3GJ0wQ%3D%3D</t>
         </is>
       </c>
     </row>
